--- a/simulation/simulation-economique.xlsx
+++ b/simulation/simulation-economique.xlsx
@@ -15,8 +15,11 @@
     <sheet name="Scénarios" sheetId="5" state="visible" r:id="rId7"/>
     <sheet name="Sensibilité" sheetId="6" state="visible" r:id="rId8"/>
     <sheet name="Vacance prudente" sheetId="7" state="visible" r:id="rId9"/>
+    <sheet name="Argumentaire" sheetId="8" state="visible" r:id="rId10"/>
+    <sheet name="Acteurs" sheetId="9" state="visible" r:id="rId11"/>
   </sheets>
   <definedNames>
+    <definedName function="false" hidden="true" localSheetId="8" name="_xlnm._FilterDatabase" vbProcedure="false">Acteurs!$A$4:$I$20</definedName>
     <definedName function="false" hidden="true" localSheetId="4" name="_xlnm._FilterDatabase" vbProcedure="false">Scénarios!$A$4:$U$41</definedName>
     <definedName function="false" hidden="false" name="assurance_franchise" vbProcedure="false">Hypothèses!$C$43</definedName>
     <definedName function="false" hidden="false" name="assurance_taux" vbProcedure="false">Hypothèses!$C$42</definedName>
@@ -106,8 +109,66 @@
 </comments>
 </file>
 
+<file path=xl/comments8.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <authors>
+    <author>Unknown Author</author>
+  </authors>
+  <commentList>
+    <comment ref="C18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Estimation illustrative : vélo à 800 € sur 10 ans, entretien et antivol, environ 20 à 25 €/mois.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="C19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Estimation illustrative : vélo-cargo de 3 500 à 7 000 €, batterie de 500 à 1 000 € tous les 4 à 5 ans, entretien professionnel et assurance, environ 100 à 120 €/mois.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D18" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Véligo Location 2026, vélo mécanique (Île-de-France Mobilités).</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="D19" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <sz val="10"/>
+            <rFont val="Arial"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">Véligo Location 2026, vélo-cargo : jusqu'à 88 €/mois, subventionné.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="591" uniqueCount="461">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="776" uniqueCount="628">
   <si>
     <t xml:space="preserve">Pignon commun — simulation économique du fonds commun en location</t>
   </si>
@@ -136,6 +197,12 @@
     <t xml:space="preserve">Vacance prudente — effet d'un tarif calculé en supposant moins de vélos loués que prévu, face à plusieurs réalités.</t>
   </si>
   <si>
+    <t xml:space="preserve">Argumentaire — comparaison avec l'achat, un loueur privé et une location publique, prix mensuels liés à la feuille Cotisation, faiblesses d'un loueur classique, raisons de choisir Pignon commun et objections.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acteurs — les acteurs à rencontrer, ce qu'il faut leur demander, l'argument à mettre en avant et des colonnes de suivi des contacts à remplir.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Légende</t>
   </si>
   <si>
@@ -1490,13 +1557,508 @@
   </si>
   <si>
     <t xml:space="preserve">Lecture : supposer 80 % d'occupation au lieu de 94 % relève les prix d'environ 5 % et réduit fortement le risque dans les tempêtes ; la révision annuelle fait ensuite redescendre le tarif si la vacance ne se produit pas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pourquoi louer à Pignon commun plutôt qu'ailleurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arguments de la page de présentation et du registre des acteurs (docs/acteurs.md). Les prix Pignon commun sont liés à la feuille Cotisation.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Comparaison avec les autres solutions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Critère</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pignon commun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acheter son vélo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Loueur privé par abonnement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Location publique (type Véligo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Propriétaire du vélo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La coopérative, dont l'usager est sociétaire</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'usager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'entreprise de location</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La collectivité, via un exploitant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ce que paie l'usager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une part fixe et une part au kilomètre : l'usure qu'il cause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le vélo d'avance, puis chaque réparation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un forfait mensuel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un forfait mensuel subventionné</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durée</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Engagement minimal de 12 à 24 mois, puis sans limite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Sans limite</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Selon l'offre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3 à 12 mois</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le fabricant est payé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par une rente sur la durée de vie, avec une prime s'il dure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la vente</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la vente de la flotte au loueur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À la vente de la flotte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le réparateur est payé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forfait de suivi et prime de durabilité, jamais de marge sur les pièces</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À chaque intervention</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par le loueur, selon son organisation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Par l'exploitant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Qui fixe le prix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La coopérative, sur des coûts publiés et révisés chaque année</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le marché</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'entreprise</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La collectivité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'excédent va</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dans la coopérative : baisse du tarif ou réserve commune</t>
+  </si>
+  <si>
+    <t xml:space="preserve">—</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À l'entreprise et à ses actionnaires</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Au service public, financé en partie par l'impôt</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suivi du vélo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contrôles préventifs selon le kilométrage, historique pièce par pièce</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À l'usager d'y penser</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entretien par le loueur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entretien par l'exploitant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">En fin de contrat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendu, reconditionné et reloué ; pièces valides au stock commun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revendu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rendu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prix mensuels indicatifs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pignon commun (€/mois)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coût de possession estimé (€/mois)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Véligo (€/mois)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Écart Pignon commun / possession</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Léger, vélo classique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intensif, vélo-cargo électrique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coût de possession et Véligo : valeurs saisies (bleu), modifiables. Voir les commentaires des cellules.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les deux faiblesses d'un loueur classique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Faiblesse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pourquoi</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réponse de Pignon commun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Il loue des vélos qu'il n'a pas conçus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rarement fabricant, il achète sa flotte à des fabricants payés à la vente et la fait réparer par des ateliers payés à l'intervention : des acteurs dont les intérêts ne vont pas forcément vers la durée de vie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricants, réparateurs et usagers sont dans la même coopérative et payés par le même fonds, sur le même résultat : la durée de vie. Rente et prime pour le fabricant, prime aux kilomètres sans panne pour le réparateur, pièces standard et documentées imposées par le label.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un vélo qui n'est pas le sien, on le ménage moins</t>
+  </si>
+  <si>
+    <t xml:space="preserve">L'usager ne supporte ni l'usure ni la revente. Le loueur n'a que la caution et la facture de dégâts, une fois le mal fait.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Part au kilomètre qui fait payer l'usure réelle, négligence facturée hors du fonds, état des lieux daté à l'entrée et à la sortie, engagement de signaler avant la panne, conseil d'entretien. Surtout, l'éco-usager est sociétaire : le parc qu'il abîme est en partie le sien, et chaque réparation évitée pèse sur le tarif qu'il vote.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les cinq raisons de choisir Pignon commun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Personne ne gagne à ce que le vélo casse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ni le fabricant, payé tant que le vélo roule, ni le réparateur, primé sur les kilomètres sans panne, ni la coopérative, sans actionnaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2. On paie l'usure qu'on cause</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La part au kilomètre suit l'usage réel : un mois où l'on roule peu coûte moins cher.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3. On a son mot à dire sur le prix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tarif construit sur des coûts publiés, voté et révisé chaque année ; la provision non consommée fait baisser le prix.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4. Moins d'arrêts, pas d'avance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas de vélo-cargo à 5 000 € à financer, entretien planifié avant la panne, casse prématurée garantie, atelier noté sur le délai de remise en service.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5. La cotisation construit une filière</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricants de pièces réparables, ateliers de proximité, vélo reconditionné et reloué avec son historique.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objections attendues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Objection</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Réponse</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« C'est un loueur de plus. »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un loueur subit la conception de ses vélos et la négligence de ses clients ; Pignon commun aligne fabricants, réparateurs et usagers sur la durée de vie.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« Véligo est moins cher. »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Véligo est subventionné et limité à 3 à 12 mois : c'est une offre d'essai. Pignon commun vise l'usage durable, sans limite de durée, avec une gouvernance partagée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« Posséder son vélo coûte moins cher. »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Vrai pour un usage léger (voir le tableau des prix). La cible prioritaire est l'usage intensif, où le prix rejoint le coût de possession, avec le service en plus.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« Les usagers vont abîmer des vélos qui ne sont pas à eux. »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le risque existe dans toute location ; Pignon commun y oppose la part au kilomètre, la négligence facturée, l'état des lieux et le statut de sociétaire. À vérifier en pilote avec les données de Véligo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">« Qui garantit que le fonds tient ? »</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La simulation économique : scénarios critiques, révision annuelle obligatoire, tarif de démarrage prudent et réserve d'environ 205 € par vélo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acteurs à rencontrer et suivi des contacts</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Détail des fiches dans docs/acteurs.md. Les colonnes sur fond jaune sont à remplir au fil des rencontres ; la ligne d'exemple montre le format attendu.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Priorité</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Acteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">À demander</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Argument à mettre en avant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Résultat</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prochaine étape</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Droit et assurance</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Juriste spécialisé</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La location suffit-elle à écarter la requalification en assurance ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le vélo appartient à la SCIC, qui entretient son propre parc comme un loueur de flotte.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mutuelle d'assurance de l'ESS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prix de l'assurance vol d'un parc de 2 000 vélos (simulation : 5 % de la valeur par an)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les garde-fous contre la négligence réduisent la sinistralité d'un parc loué.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financeurs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ecologic</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une réparation payée par une SCIC propriétaire ouvre-t-elle droit au Bonus Répar Cycle ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La réparation est au cœur du modèle : le réparateur est payé pour éviter la panne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fabricants</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Douze Cycles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rente sur 8 à 10 ans ? Coût de fabrication réel d'un cargo labellisé ? Garantie de disponibilité des pièces ?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenu indépendant des ventes, client qui paie la durabilité, voix dans la gouvernance. Déjà en logique de service avec Ecovelo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ateliers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">La Fabrique des Cyclistes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Être l'atelier pilote ; heures réelles par vélo et par an</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenu socle sans malus, prime de durabilité, aucune dépendance à la marge sur les pièces : payé pour éviter la panne.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ADEME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Financer l'étude de faisabilité et le pilote (dispositif EFC 2026)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un loueur classique reste dans l'économie de la vente ; Pignon commun paie sur la durée de vie : c'est l'économie de la fonctionnalité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Collectivités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Île-de-France Mobilités et Cyclonova (Véligo)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taux de casse, vol, vacance, rotation ; part des réparations due à la négligence</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Se présenter en relais de Véligo, pas en concurrent ; leurs données testent l'argument sur la négligence.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Usagers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Les Boîtes à Vélo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coût réel de possession d'un vélo-cargo ; disposition à payer un service complet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pas de vélo à 5 000 € à avancer, moins de jours d'arrêt, casse garantie : le cœur de cible.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montage</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CG Scop et union régionale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Structurer les trois collèges et financer un comité technique indépendant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Une SCIC où chaque collège vote, au service d'un bien commun.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Théorie</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ATEMIS et IEEFC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Relire le modèle avant le dossier ADEME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un cas concret d'économie de la fonctionnalité et de la coopération dans le vélo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Arcade Cycles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mêmes questions que pour Douze Cycles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revenu stable dans une filière en surcapacité.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Manufacture Française du Cycle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rôle de perma-fabricant sous-traitant payé sur la durée.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lapierre</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Conversation stratégique, pas partenaire unique</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un modèle économique autonome, recherché pendant le redressement judiciaire.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">VELOOP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Parcours de reconditionnement et stock de pièces commun</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Le vélo rendu est reconditionné et reloué, ses pièces retournent au stock.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mobilians et OPCO Mobilités</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reconnaissance des niveaux N1 à N3 ; financement de la formation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Un métier de réparateur revalorisé, payé pour la durée de vie obtenue.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FUB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Données sur le vol ; regard des usagers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Transparence sur l'usage léger, pour lequel posséder son vélo reste moins cher.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Exemple</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nom de l'acteur</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prénom Nom, fonction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">30/09/2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Intéressé, attend le dossier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Envoyer la simulation avant le 15/10</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="8">
+  <numFmts count="10">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="#,##0;\-#,##0;\-"/>
     <numFmt numFmtId="166" formatCode="0.0%;\-0.0%;\-"/>
@@ -1505,6 +2067,8 @@
     <numFmt numFmtId="169" formatCode="0.000&quot; €&quot;;\-0.000&quot; €&quot;;\-"/>
     <numFmt numFmtId="170" formatCode="0"/>
     <numFmt numFmtId="171" formatCode="#,##0.###"/>
+    <numFmt numFmtId="172" formatCode="\+0%;\-0%;0%"/>
+    <numFmt numFmtId="173" formatCode="dd/mm/yyyy"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1592,7 +2156,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1602,7 +2166,7 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF2F5D50"/>
-        <bgColor rgb="FF555555"/>
+        <bgColor rgb="FF3E6B52"/>
       </patternFill>
     </fill>
     <fill>
@@ -1621,6 +2185,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFE8F0EC"/>
         <bgColor rgb="FFD9E6DF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF3E6B52"/>
+        <bgColor rgb="FF2F5D50"/>
       </patternFill>
     </fill>
   </fills>
@@ -1667,7 +2237,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="53">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1836,6 +2406,50 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="6" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="173" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1845,7 +2459,7 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="28">
+  <dxfs count="30">
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -2069,6 +2683,22 @@
         </patternFill>
       </fill>
     </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFFFFF00"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF0000FF"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
   </dxfs>
   <colors>
     <indexedColors>
@@ -2121,7 +2751,7 @@
       <rgbColor rgb="FF555555"/>
       <rgbColor rgb="FF969696"/>
       <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
+      <rgbColor rgb="FF3E6B52"/>
       <rgbColor rgb="FF003300"/>
       <rgbColor rgb="FF333300"/>
       <rgbColor rgb="FF993300"/>
@@ -2134,6 +2764,10 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
 </file>
 
@@ -2317,7 +2951,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B23"/>
+  <dimension ref="B2:B25"/>
   <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="3"/>
@@ -2372,26 +3006,26 @@
         <v>8</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B12" s="2"/>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B12" s="2" t="s">
+        <v>9</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="3" t="s">
-        <v>9</v>
+      <c r="B13" s="2" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
+      <c r="B14" s="2"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="3" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B16" s="5" t="s">
+      <c r="B16" s="4" t="s">
         <v>12</v>
       </c>
     </row>
@@ -2401,20 +3035,20 @@
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B18" s="2"/>
+      <c r="B18" s="5" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B19" s="3" t="s">
-        <v>14</v>
+      <c r="B19" s="2" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B20" s="2" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B21" s="2" t="s">
+      <c r="B20" s="2"/>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B21" s="3" t="s">
         <v>16</v>
       </c>
     </row>
@@ -2423,9 +3057,19 @@
         <v>17</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B23" s="2" t="s">
         <v>18</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B24" s="2" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B25" s="2" t="s">
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2457,1152 +3101,1152 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" s="10" t="n">
         <v>1200</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F5" s="12" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>800</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F6" s="12" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C7" s="10" t="n">
         <v>40</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="E7" s="11" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="F7" s="12" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="C8" s="10" t="n">
         <v>2800</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E8" s="11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="F8" s="12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="C9" s="10" t="n">
         <v>5500</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="F9" s="12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C10" s="13" t="n">
         <v>0.2</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F10" s="12" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C11" s="13" t="n">
         <v>0.75</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="F11" s="12" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C12" s="14" t="n">
         <v>0.02</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F12" s="12" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C13" s="14" t="n">
         <v>0.05</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F13" s="12" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C14" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F14" s="12" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C15" s="15" t="n">
         <v>440</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="F15" s="12" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C16" s="16" t="n">
         <v>1170</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="F16" s="12" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C17" s="10" t="n">
         <v>10</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F17" s="12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C18" s="10" t="n">
         <v>8</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F18" s="12" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C19" s="14" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="F19" s="12" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C20" s="17" t="n">
         <v>1.17857142857143</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="F20" s="12" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C21" s="17" t="n">
         <v>1.16363636363636</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="F21" s="12" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C22" s="18" t="n">
         <v>1</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="F22" s="12" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C23" s="15" t="n">
         <v>47</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="F23" s="12" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C24" s="14" t="n">
         <v>0.04</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F24" s="12" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C25" s="15" t="n">
         <v>120</v>
       </c>
       <c r="D25" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="F25" s="12" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C26" s="14" t="n">
         <v>0.3</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F26" s="12" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C27" s="10" t="n">
         <v>75</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="F27" s="12" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C28" s="14" t="n">
         <v>0.25</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E28" s="11" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="F28" s="12" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="C29" s="14" t="n">
         <v>0.16</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="F29" s="12" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C30" s="19" t="n">
         <v>0.025</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E30" s="11" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="F30" s="12" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C31" s="19" t="n">
         <v>0.045</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="F31" s="12" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C32" s="18" t="n">
         <v>1</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="F32" s="12" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="C33" s="15" t="n">
         <v>650</v>
       </c>
       <c r="D33" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="F33" s="12" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C34" s="17" t="n">
         <v>1.05</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="E34" s="11" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="F34" s="12" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C35" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E35" s="11" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="F35" s="12" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C36" s="14" t="n">
         <v>0.015</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F36" s="12" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C37" s="14" t="n">
         <v>0.03</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F37" s="12" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C38" s="15" t="n">
         <v>400</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F38" s="12" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="C39" s="17" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F39" s="12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="C40" s="14" t="n">
         <v>0.02</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E40" s="11" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="F40" s="12" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C41" s="14" t="n">
         <v>0.04</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E41" s="11" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="F41" s="12" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C42" s="14" t="n">
         <v>0.05</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E42" s="11" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="F42" s="12" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C43" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E43" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F43" s="12" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C44" s="15" t="n">
         <v>150</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E44" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F44" s="12" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C45" s="15" t="n">
         <v>300</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E45" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F45" s="12" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C46" s="14" t="n">
         <v>0.6</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E46" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F46" s="12" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C47" s="15" t="n">
         <v>25</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E47" s="11" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="F47" s="12" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C48" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="E48" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F48" s="12" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C49" s="15" t="n">
         <v>60</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E49" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F49" s="12" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C50" s="15" t="n">
         <v>120</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F50" s="12" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C51" s="14" t="n">
         <v>0.06</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E51" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C52" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E52" s="11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="F52" s="12" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C53" s="14" t="n">
         <v>0.08</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E53" s="11" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="F53" s="12" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C54" s="14" t="n">
         <v>0.02</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E54" s="11" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="F54" s="12" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C55" s="20" t="n">
         <v>1</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="E55" s="11" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C56" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E56" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F56" s="12" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C57" s="14" t="n">
         <v>0.1</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="E57" s="11" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="F57" s="12" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C58" s="15" t="n">
         <v>0</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="E58" s="11" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="F58" s="12" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C59" s="15" t="n">
         <v>431</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E59" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F59" s="12" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C60" s="15" t="n">
         <v>765</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E60" s="11" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
     </row>
   </sheetData>
@@ -3632,29 +4276,29 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="8" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="B3" s="8"/>
       <c r="C3" s="8" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="21" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
@@ -3662,7 +4306,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="C5" s="24" t="n">
         <f aca="false">remplissage/(churn+remplissage-churn*remplissage)</f>
@@ -3675,7 +4319,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="C6" s="25" t="n">
         <f aca="false">C5*km_leger</f>
@@ -3688,7 +4332,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C7" s="26" t="n">
         <f aca="false">(vie_leger-1)/2</f>
@@ -3701,7 +4345,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C8" s="26" t="n">
         <f aca="false">h_1000km_leger*h_facteur/1000*C6*(1+vieillissement*C7)</f>
@@ -3714,7 +4358,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="21" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="B9" s="22"/>
       <c r="C9" s="22"/>
@@ -3722,7 +4366,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C10" s="27" t="n">
         <f aca="false">forfait_suivi*(C5+forfait_vacant*(1-C5))</f>
@@ -3735,7 +4379,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C11" s="27" t="n">
         <f aca="false">C8*taux_horaire</f>
@@ -3748,7 +4392,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="C12" s="27" t="n">
         <f aca="false">prime_rep*(C10+C11)*score_moyen/100</f>
@@ -3761,7 +4405,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="23" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C13" s="27" t="n">
         <f aca="false">pieces_km_leger*pieces_facteur*C6</f>
@@ -3774,7 +4418,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="23" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="C14" s="27" t="n">
         <f aca="false">0</f>
@@ -3787,7 +4431,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="C15" s="27" t="n">
         <f aca="false">IF(taux_financement&gt;0,cout_leger*taux_financement/(1-(1+taux_financement)^(-vie_leger)),cout_leger/vie_leger)</f>
@@ -3800,7 +4444,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="23" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="C16" s="27" t="n">
         <f aca="false">prime_fab*C15*score_moyen/75</f>
@@ -3813,7 +4457,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="C17" s="27" t="n">
         <f aca="false">casse_leger*casse_facteur*C5*casse_cout</f>
@@ -3826,7 +4470,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C18" s="27" t="n">
         <f aca="false">assurance_taux*cout_leger+vol_leger*(C5+0.3*(1-C5))*assurance_franchise*cout_leger-vol_leger*C5*franchise_client_leger*recouvrement_franchise</f>
@@ -3839,7 +4483,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="C19" s="27" t="n">
         <f aca="false">capteur_cout*(1/vie_leger+capteur_renouvellement)</f>
@@ -3852,7 +4496,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="C20" s="27" t="n">
         <f aca="false">churn*C5*recond_leger</f>
@@ -3865,7 +4509,7 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="28" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="C21" s="29" t="n">
         <f aca="false">SUM(C10:C20)</f>
@@ -3878,7 +4522,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="21" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="B22" s="22"/>
       <c r="C22" s="22"/>
@@ -3886,7 +4530,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="23" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="C23" s="27" t="n">
         <f aca="false">C11+C13+prime_rep*C11*score_moyen/100</f>
@@ -3899,7 +4543,7 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="23" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" s="27" t="n">
         <f aca="false">C21-C23+gestion_fixe/(n_leger+n_intensif)</f>
@@ -3912,7 +4556,7 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="23" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="C25" s="26" t="n">
         <f aca="false">1+gestion_taux+provision</f>
@@ -3925,7 +4569,7 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="28" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C26" s="29" t="n">
         <f aca="false">C24*C25/(C5*(1-impayes))</f>
@@ -3938,7 +4582,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="28" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="C27" s="30" t="n">
         <f aca="false">C23*C25/(C5*(1-impayes)*km_leger*(1-fraude_part*fraude_sous_declaration))</f>
@@ -3951,7 +4595,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="28" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="C28" s="29" t="n">
         <f aca="false">C26+C27*km_leger</f>
@@ -3964,7 +4608,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="28" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="C29" s="29" t="n">
         <f aca="false">C28/12</f>
@@ -3977,7 +4621,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="23" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C30" s="27" t="n">
         <f aca="false">(C26+C27*km_leger*(1-fraude_part*fraude_sous_declaration))*(1-impayes)</f>
@@ -3990,7 +4634,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="21" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B31" s="22"/>
       <c r="C31" s="22"/>
@@ -3998,7 +4642,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="23" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C32" s="31" t="n">
         <f aca="false">page_leger</f>
@@ -4011,7 +4655,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="23" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="C33" s="24" t="n">
         <f aca="false">C28/C32-1</f>
@@ -4047,17 +4691,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="32" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="B4" s="33" t="n">
         <v>1</v>
@@ -4092,7 +4736,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="B5" s="26" t="n">
         <f aca="false">(1+inflation)^(B4-1)</f>
@@ -4137,7 +4781,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B6" s="31" t="n">
         <f aca="false">Cotisation!$C$21*n_leger*B5</f>
@@ -4182,7 +4826,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="B7" s="31" t="n">
         <f aca="false">Cotisation!$D$21*n_intensif*B5</f>
@@ -4227,7 +4871,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="B8" s="27" t="n">
         <f aca="false">gestion_taux*(B6+B7)+gestion_fixe*B5</f>
@@ -4272,7 +4916,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="28" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B9" s="29" t="n">
         <f aca="false">SUM(B6:B8)</f>
@@ -4317,7 +4961,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="23" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="B10" s="26" t="n">
         <f aca="false">1</f>
@@ -4362,7 +5006,7 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="23" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="B11" s="31" t="n">
         <f aca="false">Cotisation!$C$30*n_leger*Cotisation!$C$5*B10</f>
@@ -4407,7 +5051,7 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="23" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="B12" s="31" t="n">
         <f aca="false">Cotisation!$D$30*n_intensif*Cotisation!$D$5*B10</f>
@@ -4452,7 +5096,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="28" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="B13" s="29" t="n">
         <f aca="false">B11+B12</f>
@@ -4497,7 +5141,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="28" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B14" s="29" t="n">
         <f aca="false">B13-B9</f>
@@ -4542,7 +5186,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="23" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B15" s="24" t="n">
         <f aca="false">IF(B13=0,0,B14/B13)</f>
@@ -4587,7 +5231,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="28" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="B16" s="29" t="n">
         <f aca="false">capital_initial+B14</f>
@@ -4632,7 +5276,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="23" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B17" s="31" t="n">
         <f aca="false">Cotisation!$C$29*B10</f>
@@ -4677,7 +5321,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="23" t="s">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="B18" s="31" t="n">
         <f aca="false">Cotisation!$D$29*B10</f>
@@ -4722,7 +5366,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="23" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="B19" s="31" t="n">
         <f aca="false">(SUM(Cotisation!$C$10:$C$12)*n_leger+SUM(Cotisation!$D$10:$D$12)*n_intensif)*B5/n_ateliers</f>
@@ -4767,7 +5411,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="23" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B20" s="31" t="n">
         <f aca="false">(Cotisation!$C$15+Cotisation!$C$16)*n_leger+(Cotisation!$D$15+Cotisation!$D$16)*n_intensif</f>
@@ -4812,7 +5456,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="28" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="B22" s="34" t="n">
         <f aca="false">MIN(B16:K16)</f>
@@ -4821,7 +5465,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="28" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="B23" s="35" t="n">
         <f aca="false">SUM(B14:K14)/SUM(B13:K13)</f>
@@ -4864,88 +5508,88 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="8" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="C4" s="8" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D4" s="8" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="E4" s="8" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="J4" s="8" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="K4" s="8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="L4" s="8" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="M4" s="8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="N4" s="8" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="O4" s="8" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="P4" s="8" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="Q4" s="8" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="R4" s="8" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="S4" s="8" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="T4" s="8" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="U4" s="8" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="9" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C5" s="36" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="D5" s="24" t="n">
         <v>0.09565</v>
@@ -5004,13 +5648,13 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="C6" s="36" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="D6" s="24" t="n">
         <v>1</v>
@@ -5069,13 +5713,13 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C7" s="36" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="D7" s="24" t="n">
         <v>0.00015</v>
@@ -5134,13 +5778,13 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="C8" s="36" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="D8" s="24" t="n">
         <v>0.65035</v>
@@ -5199,13 +5843,13 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="C9" s="36" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="D9" s="24" t="n">
         <v>0.0003</v>
@@ -5264,13 +5908,13 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="C10" s="36" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="D10" s="24" t="n">
         <v>0.0059</v>
@@ -5329,13 +5973,13 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="C11" s="36" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="D11" s="24" t="n">
         <v>0.54365</v>
@@ -5394,13 +6038,13 @@
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="C12" s="36" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="D12" s="24" t="n">
         <v>0.80825</v>
@@ -5459,13 +6103,13 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="C13" s="36" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="D13" s="24" t="n">
         <v>0.12735</v>
@@ -5524,13 +6168,13 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C14" s="36" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="D14" s="24" t="n">
         <v>1</v>
@@ -5548,7 +6192,7 @@
         <v>937.796442292882</v>
       </c>
       <c r="I14" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J14" s="27" t="n">
         <v>-137129.635023073</v>
@@ -5589,13 +6233,13 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="C15" s="36" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="D15" s="24" t="n">
         <v>1</v>
@@ -5613,7 +6257,7 @@
         <v>938.23809543717</v>
       </c>
       <c r="I15" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J15" s="27" t="n">
         <v>-121048.091810633</v>
@@ -5654,13 +6298,13 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C16" s="36" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="D16" s="24" t="n">
         <v>0.00115</v>
@@ -5719,13 +6363,13 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="C17" s="36" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="D17" s="24" t="n">
         <v>0.00095</v>
@@ -5784,13 +6428,13 @@
     </row>
     <row r="18" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="C18" s="36" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="D18" s="24" t="n">
         <v>0.0027</v>
@@ -5849,13 +6493,13 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="C19" s="36" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="D19" s="24" t="n">
         <v>0.0001</v>
@@ -5914,13 +6558,13 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="C20" s="36" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="D20" s="24" t="n">
         <v>0.00025</v>
@@ -5979,13 +6623,13 @@
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C21" s="36" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="D21" s="24" t="n">
         <v>0.6143</v>
@@ -6003,7 +6647,7 @@
         <v>242.168703895423</v>
       </c>
       <c r="I21" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J21" s="27" t="n">
         <v>4240.70263328583</v>
@@ -6044,13 +6688,13 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="C22" s="36" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="D22" s="24" t="n">
         <v>0.01135</v>
@@ -6109,13 +6753,13 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="D23" s="24" t="n">
         <v>0.00085</v>
@@ -6174,13 +6818,13 @@
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="D24" s="24" t="n">
         <v>0.0375</v>
@@ -6239,13 +6883,13 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="C25" s="36" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="D25" s="24" t="n">
         <v>1</v>
@@ -6304,13 +6948,13 @@
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="C26" s="36" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="D26" s="24" t="n">
         <v>0.001</v>
@@ -6369,13 +7013,13 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="C27" s="36" t="s">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="D27" s="24" t="n">
         <v>0.3026</v>
@@ -6434,13 +7078,13 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="C28" s="36" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="D28" s="24" t="n">
         <v>0.4089</v>
@@ -6458,7 +7102,7 @@
         <v>187.228080660091</v>
       </c>
       <c r="I28" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J28" s="27" t="n">
         <v>11325.2804455554</v>
@@ -6499,13 +7143,13 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="C29" s="36" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="D29" s="24" t="n">
         <v>0.0026</v>
@@ -6564,13 +7208,13 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C30" s="36" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="D30" s="24" t="n">
         <v>0.0068</v>
@@ -6629,13 +7273,13 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="C31" s="36" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="D31" s="24" t="n">
         <v>0.0002</v>
@@ -6694,13 +7338,13 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="C32" s="36" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="D32" s="24" t="n">
         <v>0.63445</v>
@@ -6759,13 +7403,13 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="C33" s="36" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="D33" s="24" t="n">
         <v>1</v>
@@ -6783,7 +7427,7 @@
         <v>2061.2392320311</v>
       </c>
       <c r="I33" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J33" s="27" t="n">
         <v>-355688.752013205</v>
@@ -6824,13 +7468,13 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="C34" s="36" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="D34" s="24" t="n">
         <v>0.03735</v>
@@ -6889,13 +7533,13 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C35" s="36" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="D35" s="24" t="n">
         <v>0</v>
@@ -6954,13 +7598,13 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="C36" s="36" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="D36" s="24" t="n">
         <v>0.24085</v>
@@ -7019,13 +7663,13 @@
     </row>
     <row r="37" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C37" s="36" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="D37" s="24" t="n">
         <v>0</v>
@@ -7084,13 +7728,13 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="C38" s="36" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="D38" s="24" t="n">
         <v>0.3055</v>
@@ -7108,7 +7752,7 @@
         <v>208.996273564093</v>
       </c>
       <c r="I38" s="26" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="J38" s="27" t="n">
         <v>14043.2662604792</v>
@@ -7149,13 +7793,13 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C39" s="36" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="D39" s="24" t="n">
         <v>0.2608</v>
@@ -7214,13 +7858,13 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C40" s="36" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="D40" s="24" t="n">
         <v>0.3397</v>
@@ -7279,13 +7923,13 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C41" s="36" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="D41" s="24" t="n">
         <v>0.07455</v>
@@ -7344,12 +7988,12 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="7" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="7" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
     </row>
   </sheetData>
@@ -7394,17 +8038,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="23" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="B4" s="37" t="n">
         <v>0.882043</v>
@@ -7412,7 +8056,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="23" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B5" s="37" t="n">
         <v>0.9348</v>
@@ -7420,7 +8064,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="23" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B6" s="37" t="n">
         <v>0.8826</v>
@@ -7428,7 +8072,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="23" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="B7" s="37" t="n">
         <v>-0.172807613274633</v>
@@ -7436,7 +8080,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="23" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="B8" s="38" t="n">
         <v>3092588.60830878</v>
@@ -7444,7 +8088,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="23" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="B9" s="38" t="n">
         <v>5731522.54595835</v>
@@ -7452,25 +8096,25 @@
     </row>
     <row r="12" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -7478,7 +8122,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="C13" s="39" t="n">
         <v>1000</v>
@@ -7501,7 +8145,7 @@
         <v>2</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="C14" s="39" t="n">
         <v>0.5</v>
@@ -7524,7 +8168,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C15" s="39" t="n">
         <v>0.75</v>
@@ -7547,7 +8191,7 @@
         <v>4</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="C16" s="39" t="n">
         <v>0.55</v>
@@ -7570,7 +8214,7 @@
         <v>5</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C17" s="39" t="n">
         <v>0</v>
@@ -7593,7 +8237,7 @@
         <v>6</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="C18" s="39" t="n">
         <v>0.1</v>
@@ -7616,7 +8260,7 @@
         <v>7</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="C19" s="39" t="n">
         <v>0</v>
@@ -7639,7 +8283,7 @@
         <v>8</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="C20" s="39" t="n">
         <v>40</v>
@@ -7662,7 +8306,7 @@
         <v>9</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C21" s="39" t="n">
         <v>0.7</v>
@@ -7685,7 +8329,7 @@
         <v>10</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C22" s="39" t="n">
         <v>0</v>
@@ -7708,7 +8352,7 @@
         <v>11</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C23" s="39" t="n">
         <v>0</v>
@@ -7731,7 +8375,7 @@
         <v>12</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="C24" s="39" t="n">
         <v>0</v>
@@ -7754,7 +8398,7 @@
         <v>13</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="C25" s="39" t="n">
         <v>0.5</v>
@@ -7777,7 +8421,7 @@
         <v>14</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="C26" s="39" t="n">
         <v>0</v>
@@ -7800,7 +8444,7 @@
         <v>15</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="C27" s="39" t="n">
         <v>380</v>
@@ -7823,7 +8467,7 @@
         <v>16</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C28" s="39" t="n">
         <v>0</v>
@@ -7846,7 +8490,7 @@
         <v>17</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C29" s="39" t="n">
         <v>60</v>
@@ -7869,7 +8513,7 @@
         <v>18</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="C30" s="39" t="n">
         <v>0</v>
@@ -7892,7 +8536,7 @@
         <v>19</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="C31" s="39" t="n">
         <v>0.5</v>
@@ -7915,7 +8559,7 @@
         <v>20</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="C32" s="39" t="n">
         <v>0.02</v>
@@ -7938,7 +8582,7 @@
         <v>21</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="C33" s="39" t="n">
         <v>0.01</v>
@@ -7961,7 +8605,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="C34" s="39" t="n">
         <v>0</v>
@@ -7981,32 +8625,32 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="40" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="7" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B39" s="41"/>
       <c r="C39" s="32" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="D39" s="32" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="E39" s="32" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="F39" s="32" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B40" s="28" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="C40" s="37" t="n">
         <v>0.473224852071006</v>
@@ -8023,7 +8667,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B41" s="28" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="C41" s="37" t="n">
         <v>0.678571428571429</v>
@@ -8040,7 +8684,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B42" s="28" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C42" s="37" t="n">
         <v>0.873733552631579</v>
@@ -8057,7 +8701,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B43" s="28" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="C43" s="37" t="n">
         <v>0.94171974522293</v>
@@ -8120,63 +8764,63 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="7" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="40" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D5" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I5" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J5" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K5" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L5" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M5" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B6" s="27" t="n">
         <v>52.0948770623986</v>
@@ -8217,7 +8861,7 @@
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B7" s="27" t="n">
         <v>52.9127589115019</v>
@@ -8258,7 +8902,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B8" s="27" t="n">
         <v>54.2462619263441</v>
@@ -8299,7 +8943,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B9" s="27" t="n">
         <v>56.3417666639535</v>
@@ -8340,53 +8984,53 @@
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="40" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="45" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="8" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C12" s="8" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="D12" s="8" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="E12" s="8" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="I12" s="8" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="J12" s="8" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="K12" s="8" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="L12" s="8" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="M12" s="8" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B13" s="27" t="n">
         <v>52.0948770623986</v>
@@ -8427,7 +9071,7 @@
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="B14" s="27" t="n">
         <v>52.9127589115019</v>
@@ -8468,7 +9112,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="B15" s="27" t="n">
         <v>54.2462619263441</v>
@@ -8509,7 +9153,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="B16" s="27" t="n">
         <v>56.3417666639535</v>
@@ -8550,7 +9194,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="7" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
     </row>
   </sheetData>
@@ -8586,4 +9230,889 @@
     <oddFooter/>
   </headerFooter>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:E40"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="3" style="0" width="34"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="40" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="8" t="s">
+        <v>466</v>
+      </c>
+      <c r="B5" s="42" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" s="8" t="s">
+        <v>468</v>
+      </c>
+      <c r="D5" s="8" t="s">
+        <v>469</v>
+      </c>
+      <c r="E5" s="8" t="s">
+        <v>470</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="43" t="s">
+        <v>471</v>
+      </c>
+      <c r="B6" s="44" t="s">
+        <v>472</v>
+      </c>
+      <c r="C6" s="36" t="s">
+        <v>473</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>474</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="s">
+        <v>476</v>
+      </c>
+      <c r="B7" s="44" t="s">
+        <v>477</v>
+      </c>
+      <c r="C7" s="36" t="s">
+        <v>478</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>479</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="43" t="s">
+        <v>481</v>
+      </c>
+      <c r="B8" s="44" t="s">
+        <v>482</v>
+      </c>
+      <c r="C8" s="36" t="s">
+        <v>483</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>484</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>486</v>
+      </c>
+      <c r="B9" s="44" t="s">
+        <v>487</v>
+      </c>
+      <c r="C9" s="36" t="s">
+        <v>488</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>489</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="43" t="s">
+        <v>491</v>
+      </c>
+      <c r="B10" s="44" t="s">
+        <v>492</v>
+      </c>
+      <c r="C10" s="36" t="s">
+        <v>493</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>494</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="43" t="s">
+        <v>496</v>
+      </c>
+      <c r="B11" s="44" t="s">
+        <v>497</v>
+      </c>
+      <c r="C11" s="36" t="s">
+        <v>498</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>499</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>500</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="43" t="s">
+        <v>501</v>
+      </c>
+      <c r="B12" s="44" t="s">
+        <v>502</v>
+      </c>
+      <c r="C12" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>504</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="43" t="s">
+        <v>506</v>
+      </c>
+      <c r="B13" s="44" t="s">
+        <v>507</v>
+      </c>
+      <c r="C13" s="36" t="s">
+        <v>508</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>509</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="43" t="s">
+        <v>511</v>
+      </c>
+      <c r="B14" s="44" t="s">
+        <v>512</v>
+      </c>
+      <c r="C14" s="36" t="s">
+        <v>513</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>514</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>514</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="40" t="s">
+        <v>515</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="8" t="s">
+        <v>39</v>
+      </c>
+      <c r="B17" s="8" t="s">
+        <v>516</v>
+      </c>
+      <c r="C17" s="8" t="s">
+        <v>517</v>
+      </c>
+      <c r="D17" s="8" t="s">
+        <v>518</v>
+      </c>
+      <c r="E17" s="8" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="28" t="s">
+        <v>520</v>
+      </c>
+      <c r="B18" s="45" t="n">
+        <f aca="false">Cotisation!C29</f>
+        <v>52.0948770623986</v>
+      </c>
+      <c r="C18" s="46" t="n">
+        <v>22</v>
+      </c>
+      <c r="D18" s="46" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" s="47" t="n">
+        <f aca="false">B18/C18-1</f>
+        <v>1.36794895738175</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="28" t="s">
+        <v>521</v>
+      </c>
+      <c r="B19" s="45" t="n">
+        <f aca="false">Cotisation!D29</f>
+        <v>114.190171832591</v>
+      </c>
+      <c r="C19" s="46" t="n">
+        <v>110</v>
+      </c>
+      <c r="D19" s="46" t="n">
+        <v>88</v>
+      </c>
+      <c r="E19" s="47" t="n">
+        <f aca="false">B19/C19-1</f>
+        <v>0.0380924712053721</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="7" t="s">
+        <v>522</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="40" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="8" t="s">
+        <v>524</v>
+      </c>
+      <c r="B23" s="8" t="s">
+        <v>525</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>526</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="43" t="s">
+        <v>527</v>
+      </c>
+      <c r="B24" s="36" t="s">
+        <v>528</v>
+      </c>
+      <c r="C24" s="36" t="s">
+        <v>529</v>
+      </c>
+      <c r="D24" s="36"/>
+      <c r="E24" s="36"/>
+    </row>
+    <row r="25" customFormat="false" ht="90" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="43" t="s">
+        <v>530</v>
+      </c>
+      <c r="B25" s="36" t="s">
+        <v>531</v>
+      </c>
+      <c r="C25" s="36" t="s">
+        <v>532</v>
+      </c>
+      <c r="D25" s="36"/>
+      <c r="E25" s="36"/>
+    </row>
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="40" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="48" t="s">
+        <v>534</v>
+      </c>
+      <c r="B28" s="49" t="s">
+        <v>535</v>
+      </c>
+      <c r="C28" s="49"/>
+      <c r="D28" s="49"/>
+      <c r="E28" s="49"/>
+    </row>
+    <row r="29" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="48" t="s">
+        <v>536</v>
+      </c>
+      <c r="B29" s="49" t="s">
+        <v>537</v>
+      </c>
+      <c r="C29" s="49"/>
+      <c r="D29" s="49"/>
+      <c r="E29" s="49"/>
+    </row>
+    <row r="30" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="48" t="s">
+        <v>538</v>
+      </c>
+      <c r="B30" s="49" t="s">
+        <v>539</v>
+      </c>
+      <c r="C30" s="49"/>
+      <c r="D30" s="49"/>
+      <c r="E30" s="49"/>
+    </row>
+    <row r="31" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="48" t="s">
+        <v>540</v>
+      </c>
+      <c r="B31" s="49" t="s">
+        <v>541</v>
+      </c>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+    </row>
+    <row r="32" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="48" t="s">
+        <v>542</v>
+      </c>
+      <c r="B32" s="49" t="s">
+        <v>543</v>
+      </c>
+      <c r="C32" s="49"/>
+      <c r="D32" s="49"/>
+      <c r="E32" s="49"/>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="40" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="8" t="s">
+        <v>545</v>
+      </c>
+      <c r="B35" s="8" t="s">
+        <v>546</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="43" t="s">
+        <v>547</v>
+      </c>
+      <c r="B36" s="36" t="s">
+        <v>548</v>
+      </c>
+      <c r="C36" s="36"/>
+      <c r="D36" s="36"/>
+      <c r="E36" s="36"/>
+    </row>
+    <row r="37" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="43" t="s">
+        <v>549</v>
+      </c>
+      <c r="B37" s="36" t="s">
+        <v>550</v>
+      </c>
+      <c r="C37" s="36"/>
+      <c r="D37" s="36"/>
+      <c r="E37" s="36"/>
+    </row>
+    <row r="38" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="43" t="s">
+        <v>551</v>
+      </c>
+      <c r="B38" s="36" t="s">
+        <v>552</v>
+      </c>
+      <c r="C38" s="36"/>
+      <c r="D38" s="36"/>
+      <c r="E38" s="36"/>
+    </row>
+    <row r="39" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="43" t="s">
+        <v>553</v>
+      </c>
+      <c r="B39" s="36" t="s">
+        <v>554</v>
+      </c>
+      <c r="C39" s="36"/>
+      <c r="D39" s="36"/>
+      <c r="E39" s="36"/>
+    </row>
+    <row r="40" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="43" t="s">
+        <v>555</v>
+      </c>
+      <c r="B40" s="36" t="s">
+        <v>556</v>
+      </c>
+      <c r="C40" s="36"/>
+      <c r="D40" s="36"/>
+      <c r="E40" s="36"/>
+    </row>
+  </sheetData>
+  <mergeCells count="12">
+    <mergeCell ref="C24:E24"/>
+    <mergeCell ref="C25:E25"/>
+    <mergeCell ref="B28:E28"/>
+    <mergeCell ref="B29:E29"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B31:E31"/>
+    <mergeCell ref="B32:E32"/>
+    <mergeCell ref="B36:E36"/>
+    <mergeCell ref="B37:E37"/>
+    <mergeCell ref="B38:E38"/>
+    <mergeCell ref="B39:E39"/>
+    <mergeCell ref="B40:E40"/>
+  </mergeCells>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:I22"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="9"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="22"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="0" width="30"/>
+  </cols>
+  <sheetData>
+    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="6" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="7" t="s">
+        <v>558</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="8" t="s">
+        <v>559</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C4" s="8" t="s">
+        <v>560</v>
+      </c>
+      <c r="D4" s="8" t="s">
+        <v>561</v>
+      </c>
+      <c r="E4" s="8" t="s">
+        <v>562</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>563</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>564</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>565</v>
+      </c>
+      <c r="I4" s="8" t="s">
+        <v>566</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="C5" s="43" t="s">
+        <v>568</v>
+      </c>
+      <c r="D5" s="36" t="s">
+        <v>569</v>
+      </c>
+      <c r="E5" s="36" t="s">
+        <v>570</v>
+      </c>
+      <c r="F5" s="50"/>
+      <c r="G5" s="51"/>
+      <c r="H5" s="50"/>
+      <c r="I5" s="50"/>
+    </row>
+    <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="36" t="s">
+        <v>567</v>
+      </c>
+      <c r="C6" s="43" t="s">
+        <v>571</v>
+      </c>
+      <c r="D6" s="36" t="s">
+        <v>572</v>
+      </c>
+      <c r="E6" s="36" t="s">
+        <v>573</v>
+      </c>
+      <c r="F6" s="50"/>
+      <c r="G6" s="51"/>
+      <c r="H6" s="50"/>
+      <c r="I6" s="50"/>
+    </row>
+    <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="36" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="36" t="s">
+        <v>574</v>
+      </c>
+      <c r="C7" s="43" t="s">
+        <v>575</v>
+      </c>
+      <c r="D7" s="36" t="s">
+        <v>576</v>
+      </c>
+      <c r="E7" s="36" t="s">
+        <v>577</v>
+      </c>
+      <c r="F7" s="50"/>
+      <c r="G7" s="51"/>
+      <c r="H7" s="50"/>
+      <c r="I7" s="50"/>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B8" s="36" t="s">
+        <v>578</v>
+      </c>
+      <c r="C8" s="43" t="s">
+        <v>579</v>
+      </c>
+      <c r="D8" s="36" t="s">
+        <v>580</v>
+      </c>
+      <c r="E8" s="36" t="s">
+        <v>581</v>
+      </c>
+      <c r="F8" s="50"/>
+      <c r="G8" s="51"/>
+      <c r="H8" s="50"/>
+      <c r="I8" s="50"/>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="B9" s="36" t="s">
+        <v>582</v>
+      </c>
+      <c r="C9" s="43" t="s">
+        <v>583</v>
+      </c>
+      <c r="D9" s="36" t="s">
+        <v>584</v>
+      </c>
+      <c r="E9" s="36" t="s">
+        <v>585</v>
+      </c>
+      <c r="F9" s="50"/>
+      <c r="G9" s="51"/>
+      <c r="H9" s="50"/>
+      <c r="I9" s="50"/>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="36" t="n">
+        <v>3</v>
+      </c>
+      <c r="B10" s="36" t="s">
+        <v>574</v>
+      </c>
+      <c r="C10" s="43" t="s">
+        <v>586</v>
+      </c>
+      <c r="D10" s="36" t="s">
+        <v>587</v>
+      </c>
+      <c r="E10" s="36" t="s">
+        <v>588</v>
+      </c>
+      <c r="F10" s="50"/>
+      <c r="G10" s="51"/>
+      <c r="H10" s="50"/>
+      <c r="I10" s="50"/>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B11" s="36" t="s">
+        <v>589</v>
+      </c>
+      <c r="C11" s="43" t="s">
+        <v>590</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>591</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>592</v>
+      </c>
+      <c r="F11" s="50"/>
+      <c r="G11" s="51"/>
+      <c r="H11" s="50"/>
+      <c r="I11" s="50"/>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="36" t="n">
+        <v>4</v>
+      </c>
+      <c r="B12" s="36" t="s">
+        <v>593</v>
+      </c>
+      <c r="C12" s="43" t="s">
+        <v>594</v>
+      </c>
+      <c r="D12" s="36" t="s">
+        <v>595</v>
+      </c>
+      <c r="E12" s="36" t="s">
+        <v>596</v>
+      </c>
+      <c r="F12" s="50"/>
+      <c r="G12" s="51"/>
+      <c r="H12" s="50"/>
+      <c r="I12" s="50"/>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B13" s="36" t="s">
+        <v>597</v>
+      </c>
+      <c r="C13" s="43" t="s">
+        <v>598</v>
+      </c>
+      <c r="D13" s="36" t="s">
+        <v>599</v>
+      </c>
+      <c r="E13" s="36" t="s">
+        <v>600</v>
+      </c>
+      <c r="F13" s="50"/>
+      <c r="G13" s="51"/>
+      <c r="H13" s="50"/>
+      <c r="I13" s="50"/>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="36" t="n">
+        <v>5</v>
+      </c>
+      <c r="B14" s="36" t="s">
+        <v>601</v>
+      </c>
+      <c r="C14" s="43" t="s">
+        <v>602</v>
+      </c>
+      <c r="D14" s="36" t="s">
+        <v>603</v>
+      </c>
+      <c r="E14" s="36" t="s">
+        <v>604</v>
+      </c>
+      <c r="F14" s="50"/>
+      <c r="G14" s="51"/>
+      <c r="H14" s="50"/>
+      <c r="I14" s="50"/>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B15" s="36" t="s">
+        <v>578</v>
+      </c>
+      <c r="C15" s="43" t="s">
+        <v>605</v>
+      </c>
+      <c r="D15" s="36" t="s">
+        <v>606</v>
+      </c>
+      <c r="E15" s="36" t="s">
+        <v>607</v>
+      </c>
+      <c r="F15" s="50"/>
+      <c r="G15" s="51"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="50"/>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B16" s="36" t="s">
+        <v>578</v>
+      </c>
+      <c r="C16" s="43" t="s">
+        <v>608</v>
+      </c>
+      <c r="D16" s="36" t="s">
+        <v>606</v>
+      </c>
+      <c r="E16" s="36" t="s">
+        <v>609</v>
+      </c>
+      <c r="F16" s="50"/>
+      <c r="G16" s="51"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="50"/>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B17" s="36" t="s">
+        <v>578</v>
+      </c>
+      <c r="C17" s="43" t="s">
+        <v>610</v>
+      </c>
+      <c r="D17" s="36" t="s">
+        <v>611</v>
+      </c>
+      <c r="E17" s="36" t="s">
+        <v>612</v>
+      </c>
+      <c r="F17" s="50"/>
+      <c r="G17" s="51"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="50"/>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B18" s="36" t="s">
+        <v>582</v>
+      </c>
+      <c r="C18" s="43" t="s">
+        <v>613</v>
+      </c>
+      <c r="D18" s="36" t="s">
+        <v>614</v>
+      </c>
+      <c r="E18" s="36" t="s">
+        <v>615</v>
+      </c>
+      <c r="F18" s="50"/>
+      <c r="G18" s="51"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="50"/>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B19" s="36" t="s">
+        <v>582</v>
+      </c>
+      <c r="C19" s="43" t="s">
+        <v>616</v>
+      </c>
+      <c r="D19" s="36" t="s">
+        <v>617</v>
+      </c>
+      <c r="E19" s="36" t="s">
+        <v>618</v>
+      </c>
+      <c r="F19" s="50"/>
+      <c r="G19" s="51"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="50"/>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="36" t="s">
+        <v>503</v>
+      </c>
+      <c r="B20" s="36" t="s">
+        <v>593</v>
+      </c>
+      <c r="C20" s="43" t="s">
+        <v>619</v>
+      </c>
+      <c r="D20" s="36" t="s">
+        <v>620</v>
+      </c>
+      <c r="E20" s="36" t="s">
+        <v>621</v>
+      </c>
+      <c r="F20" s="50"/>
+      <c r="G20" s="51"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="50"/>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="7" t="s">
+        <v>622</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>623</v>
+      </c>
+      <c r="F22" s="52" t="s">
+        <v>624</v>
+      </c>
+      <c r="G22" s="52" t="s">
+        <v>625</v>
+      </c>
+      <c r="H22" s="52" t="s">
+        <v>626</v>
+      </c>
+      <c r="I22" s="52" t="s">
+        <v>627</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:I20"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+  <drawing r:id="rId1"/>
+</worksheet>
 </file>